--- a/out/global_metric/excel/swin.xlsx
+++ b/out/global_metric/excel/swin.xlsx
@@ -496,25 +496,29 @@
         <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9583333134651184</v>
+        <v>0.7334465384483337</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9551127854479547</v>
+        <v>0.7333696582896134</v>
       </c>
       <c r="D2" t="n">
-        <v>58</v>
+        <v>211</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="G2" t="n">
-        <v>103</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>221</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8189669087974173</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8084591638797117</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>swin</t>
@@ -534,25 +538,29 @@
         <v>38</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9345238208770752</v>
+        <v>0.7623090147972107</v>
       </c>
       <c r="C3" t="n">
-        <v>0.93079428765965</v>
+        <v>0.7622260618729018</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>219</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="G3" t="n">
-        <v>98</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>230</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8485587455321113</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8381290150765942</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>swin</t>
@@ -572,25 +580,29 @@
         <v>61</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9642857313156128</v>
+        <v>0.7640067934989929</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9619047567837744</v>
+        <v>0.7639632420765939</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>229</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="G4" t="n">
-        <v>102</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>221</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8625273838348899</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8649498313788975</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>swin</t>
@@ -610,25 +622,29 @@
         <v>84</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9226190447807312</v>
+        <v>0.7657045722007751</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9171943076820006</v>
+        <v>0.765687693881395</v>
       </c>
       <c r="D5" t="n">
-        <v>56</v>
+        <v>228</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="G5" t="n">
-        <v>99</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>223</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.855770782889427</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8345847711492506</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>swin</t>
@@ -648,25 +664,29 @@
         <v>107</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9642857313156128</v>
+        <v>0.7640067934989929</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9623599650072854</v>
+        <v>0.7638325134037941</v>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>217</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>233</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.841415888389254</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8269878546437115</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>swin</t>
@@ -762,25 +782,29 @@
         <v>16</v>
       </c>
       <c r="B2" t="n">
-        <v>0.976190447807312</v>
+        <v>0.7470288872718811</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9746031694804738</v>
+        <v>0.7459715068463086</v>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>201</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="G2" t="n">
-        <v>103</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>239</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.835477919981552</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8139783821888227</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>swin</t>
@@ -800,25 +824,29 @@
         <v>39</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9464285969734192</v>
+        <v>0.7758913636207581</v>
       </c>
       <c r="C3" t="n">
-        <v>0.943035823536655</v>
+        <v>0.7758751852329241</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>226</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8583362158422692</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8560359074535738</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>swin</t>
@@ -838,25 +866,29 @@
         <v>62</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9642857313156128</v>
+        <v>0.755517840385437</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9621394179557704</v>
+        <v>0.7555171170774819</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>222</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>101</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>223</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8494638533379454</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8429796493387425</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>swin</t>
@@ -876,25 +908,29 @@
         <v>85</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9404761791229248</v>
+        <v>0.7640067934989929</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9368990333437516</v>
+        <v>0.7632177874211532</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>208</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="G5" t="n">
-        <v>99</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>242</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8375417963795688</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8160790710320343</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>swin</t>
@@ -914,25 +950,29 @@
         <v>108</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9583333134651184</v>
+        <v>0.7775891423225403</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9559599993740974</v>
+        <v>0.7775250006699186</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>224</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>234</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8570967369998845</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.85204422539789</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>swin</t>

--- a/out/global_metric/excel/swin.xlsx
+++ b/out/global_metric/excel/swin.xlsx
@@ -496,28 +496,28 @@
         <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7334465384483337</v>
+        <v>0.7674023509025574</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7333696582896134</v>
+        <v>0.7673594543483946</v>
       </c>
       <c r="D2" t="n">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="E2" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="G2" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8189669087974173</v>
+        <v>0.8316614781505823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8084591638797117</v>
+        <v>0.8140700528219893</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -538,28 +538,28 @@
         <v>38</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7623090147972107</v>
+        <v>0.7911714911460876</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7622260618729018</v>
+        <v>0.7911497996641556</v>
       </c>
       <c r="D3" t="n">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="E3" t="n">
         <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
         <v>230</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8485587455321113</v>
+        <v>0.858013374841462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8381290150765942</v>
+        <v>0.8422103048564487</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -580,28 +580,28 @@
         <v>61</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7640067934989929</v>
+        <v>0.7928692698478699</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7639632420765939</v>
+        <v>0.7927683135428868</v>
       </c>
       <c r="D4" t="n">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E4" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8625273838348899</v>
+        <v>0.8668050270955839</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8649498313788975</v>
+        <v>0.8546509852763834</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -622,28 +622,28 @@
         <v>84</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7657045722007751</v>
+        <v>0.7894737124443054</v>
       </c>
       <c r="C5" t="n">
-        <v>0.765687693881395</v>
+        <v>0.7894730723397902</v>
       </c>
       <c r="D5" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G5" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="H5" t="n">
-        <v>0.855770782889427</v>
+        <v>0.8583592759137554</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8345847711492506</v>
+        <v>0.8318997026302922</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -664,28 +664,28 @@
         <v>107</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7640067934989929</v>
+        <v>0.7792869210243225</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7638325134037941</v>
+        <v>0.7789498552544383</v>
       </c>
       <c r="D6" t="n">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F6" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="H6" t="n">
-        <v>0.841415888389254</v>
+        <v>0.8731350167185519</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8269878546437115</v>
+        <v>0.8751511144862025</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -782,28 +782,28 @@
         <v>16</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7470288872718811</v>
+        <v>0.7623090147972107</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7459715068463086</v>
+        <v>0.7623028268164266</v>
       </c>
       <c r="D2" t="n">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="F2" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="G2" t="n">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="H2" t="n">
-        <v>0.835477919981552</v>
+        <v>0.841312118067566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8139783821888227</v>
+        <v>0.825066692051751</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -824,28 +824,28 @@
         <v>39</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7758913636207581</v>
+        <v>0.7860780954360962</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7758751852329241</v>
+        <v>0.7860774768135594</v>
       </c>
       <c r="D3" t="n">
+        <v>232</v>
+      </c>
+      <c r="E3" t="n">
+        <v>64</v>
+      </c>
+      <c r="F3" t="n">
+        <v>62</v>
+      </c>
+      <c r="G3" t="n">
         <v>231</v>
       </c>
-      <c r="E3" t="n">
-        <v>69</v>
-      </c>
-      <c r="F3" t="n">
-        <v>63</v>
-      </c>
-      <c r="G3" t="n">
-        <v>226</v>
-      </c>
       <c r="H3" t="n">
-        <v>0.8583362158422692</v>
+        <v>0.8684480571889773</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8560359074535738</v>
+        <v>0.862064806186231</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -866,28 +866,28 @@
         <v>62</v>
       </c>
       <c r="B4" t="n">
-        <v>0.755517840385437</v>
+        <v>0.8132427930831909</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7555171170774819</v>
+        <v>0.8131776189652308</v>
       </c>
       <c r="D4" t="n">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8494638533379454</v>
+        <v>0.8937968407702064</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8429796493387425</v>
+        <v>0.8804866998630743</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -908,28 +908,28 @@
         <v>85</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7640067934989929</v>
+        <v>0.7521222233772278</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7632177874211532</v>
+        <v>0.7517436842121537</v>
       </c>
       <c r="D5" t="n">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="F5" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8375417963795688</v>
+        <v>0.8494523233022023</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8160790710320343</v>
+        <v>0.8371034279562386</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -950,28 +950,28 @@
         <v>108</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7775891423225403</v>
+        <v>0.7572156190872192</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7775250006699186</v>
+        <v>0.7568764256159537</v>
       </c>
       <c r="D6" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8570967369998845</v>
+        <v>0.855770782889427</v>
       </c>
       <c r="I6" t="n">
-        <v>0.85204422539789</v>
+        <v>0.8540008624061667</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
